--- a/data/trending_integrated_20260917_10.xlsx
+++ b/data/trending_integrated_20260917_10.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>지분 매수 공시 부재 속 가격 조작 의혹 제기. BPS 기반 저평가 주장.</t>
+          <t>낮은 BPS와 시가총액, 지분 매수 공시 부재 속 상장폐지 우려 및 주가 하락에 대한 회의적인 시각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['지분매수공시', 'BPS', '주가조작']</t>
+          <t>['BPS', '상장폐지', '지분매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,27 +659,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22750</v>
+        <v>22300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.58%</t>
+          <t>'+31.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="H3" t="n">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>18560</v>
+        <v>16950</v>
       </c>
       <c r="K3" t="n">
-        <v>19260</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>22950</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>18920</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>1.92</v>
       </c>
       <c r="O3" t="n">
-        <v>161965667070</v>
+        <v>180474000000</v>
       </c>
       <c r="P3" t="n">
-        <v>59600</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>-45000</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자회사 수주 및 미국 광통신주 급등에 따른 CPO 관련주로 부각. 데이터센터 대장 및 거래대금 1위 등극.</t>
+          <t>자회사 CPO 생산 장비 수주 및 광통신 섹터 대장주로서의 부각, 거래량 상위 기록.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['CPO', '수주', '데이터센터']</t>
+          <t>['CPO', '광통신', '수주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4095</v>
+        <v>4130</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.64%</t>
+          <t>'+7.55%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="F4" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G4" t="n">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="H4" t="n">
         <v>0.95</v>
@@ -794,7 +794,7 @@
         <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>105033163521</v>
+        <v>107623063405</v>
       </c>
       <c r="P4" t="n">
         <v>6900</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오 인수 및 소프트뱅크 관련 루머로 인한 텐버거(10배 상승) 기대감. 물량 잠김 현상 및 차익실현 가능성 언급.</t>
+          <t>카카오 인수 가능성 및 소프트뱅크 관련 호재로 인한 텐버거 기대감 속 물량 잠김 현상.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
+          <t>['카카오', '인수', '텐버거']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10630</v>
+        <v>10670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.62%</t>
+          <t>'+7.02%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.58</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G5" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="H5" t="n">
         <v>1.25</v>
@@ -886,7 +886,7 @@
         <v>0.67</v>
       </c>
       <c r="O5" t="n">
-        <v>142053943645</v>
+        <v>146316884275</v>
       </c>
       <c r="P5" t="n">
         <v>15960</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료 관련주로 주목받으며 정책주로 분류. 2만원 돌파 기대감 있으나, 주체 세력 이탈 및 개인 투자자 손실 언급.</t>
+          <t>낙태약 및 탈모 치료 관련 수혜 기대감 속 개인 투자자 매물 출회. 하지만 주가 상승 및 하락에 대한 엇갈린 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '정책주']</t>
+          <t>['낙태약', '탈모치료', '수혜주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3665</v>
+        <v>3705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.71%</t>
+          <t>'+5.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>51715543623</v>
+        <v>53489863119</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>스페이스X 이슈 언급에도 불구하고 우주 섹터 내 낙폭 과대로 인한 하락세 지속. 프로그램 매도 및 외국인 움직임 주목.</t>
+          <t>프로그램 매도세 및 우주 섹터 약세 속 투자자들의 경계심 고조와 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '낙폭', '프로그램매도']</t>
+          <t>['우주섹터', '프로그램매도', '낙폭']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21100</v>
+        <v>21250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.46%</t>
+          <t>'+5.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1061,7 +1061,7 @@
         <v>20450</v>
       </c>
       <c r="L7" t="n">
-        <v>21100</v>
+        <v>21300</v>
       </c>
       <c r="M7" t="n">
         <v>20450</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>17924873275</v>
+        <v>23875744450</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 투자의견 '매수' 목표주가 4만원 유지. 경쟁사 강세 및 주가 변동성에 대한 언급.</t>
+          <t>나스닥 반등 및 중공업 업종 강세 속 목표주가 4만원 유지 리포트와 함께 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['투자의견', '목표주가', '나스닥']</t>
+          <t>['중공업', '목표주가', '나스닥']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,79 +1115,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85700</v>
+        <v>16510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.55%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>2.93</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G8" t="n">
-        <v>488</v>
+        <v>752</v>
       </c>
       <c r="H8" t="n">
-        <v>23.27</v>
+        <v>4.88</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>83800</v>
+        <v>16100</v>
       </c>
       <c r="K8" t="n">
-        <v>84700</v>
+        <v>16200</v>
       </c>
       <c r="L8" t="n">
-        <v>86000</v>
+        <v>16750</v>
       </c>
       <c r="M8" t="n">
-        <v>84100</v>
+        <v>15560</v>
       </c>
       <c r="N8" t="n">
-        <v>23.37</v>
+        <v>1.95</v>
       </c>
       <c r="O8" t="n">
-        <v>50447649250</v>
+        <v>217345702895</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R8" t="n">
-        <v>-75000</v>
+        <v>-173000</v>
       </c>
       <c r="S8" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 투자 대비 전력 부족 가능성 제기. FOMC 악재 소멸 및 금리 인상 관련 언급.</t>
+          <t>미국 광통신주 강세에 따른 동반 상승 기대감 및 세계적 통신장비 부족 호재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '금리 인상', '원전']</t>
+          <t>['광통신', '통신장비', '호재']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16310</v>
+        <v>85700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.30%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.93</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>501</v>
       </c>
       <c r="H9" t="n">
-        <v>4.88</v>
+        <v>23.27</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>16100</v>
+        <v>83800</v>
       </c>
       <c r="K9" t="n">
-        <v>16200</v>
+        <v>84700</v>
       </c>
       <c r="L9" t="n">
-        <v>16750</v>
+        <v>86000</v>
       </c>
       <c r="M9" t="n">
-        <v>15560</v>
+        <v>84100</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>23.37</v>
       </c>
       <c r="O9" t="n">
-        <v>201648370745</v>
+        <v>53951128550</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>-173000</v>
+        <v>-75000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 동반 상승 기대감. 세계적 통신 장비 부족 호재 언급 및 2만원 돌파 목표.</t>
+          <t>AI 투자 대비 전력 부족 가능성 제기. FOMC 악재 소멸 및 금리 인상 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '통신장비', '호재']</t>
+          <t>['AI', '금리 인상', '원전']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18680</v>
+        <v>18690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'+0.65%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.21</v>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F10" t="n">
         <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="H10" t="n">
         <v>10.85</v>
@@ -1346,7 +1346,7 @@
         <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>24497082645</v>
+        <v>26304216135</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254000</v>
+        <v>255000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G11" t="n">
-        <v>2587</v>
+        <v>2349</v>
       </c>
       <c r="H11" t="n">
         <v>46.52</v>
@@ -1438,7 +1438,7 @@
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>719437779750</v>
+        <v>784741260500</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 금리 인하 및 반도체 업황 개선 기대감 속에서도 정치적 이슈와 관련된 부정적 언급 다수.</t>
+          <t>정치적 이슈와 금리 인상 우려 속에서 반도체 업황에 대한 단기적 긍정 전망 및 경계 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['금리인하', '반도체', '악재해소']</t>
+          <t>['금리인상', '반도체', '메모리']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3505</v>
+        <v>1759000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.43%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>456</v>
       </c>
       <c r="G12" t="n">
-        <v>203</v>
+        <v>1550</v>
       </c>
       <c r="H12" t="n">
-        <v>2.26</v>
+        <v>50.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3520</v>
+        <v>1759000</v>
       </c>
       <c r="K12" t="n">
-        <v>3730</v>
+        <v>1770000</v>
       </c>
       <c r="L12" t="n">
-        <v>3750</v>
+        <v>1785000</v>
       </c>
       <c r="M12" t="n">
-        <v>3460</v>
+        <v>1735000</v>
       </c>
       <c r="N12" t="n">
-        <v>3.11</v>
+        <v>50.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4046731113</v>
+        <v>1508424079500</v>
       </c>
       <c r="P12" t="n">
-        <v>16110</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>2300</v>
+        <v>333000</v>
       </c>
       <c r="R12" t="n">
-        <v>-276000</v>
+        <v>-172000</v>
       </c>
       <c r="S12" t="n">
-        <v>-9000</v>
+        <v>-24000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>차익 실현 및 하락세 전망. 상장 폐지 및 폭락 가능성 언급.</t>
+          <t>미국 증시 상승 및 악재 해소 기대감 속 자사주 매수 통한 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['차익실현', '하락', '상장폐지']</t>
+          <t>['자사주매수', '악재해소', '반도체']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1750000</v>
+        <v>3515</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.51%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
-        <v>458</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>1589</v>
+        <v>207</v>
       </c>
       <c r="H13" t="n">
-        <v>50.2</v>
+        <v>2.26</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1759000</v>
+        <v>3520</v>
       </c>
       <c r="K13" t="n">
-        <v>1770000</v>
+        <v>3730</v>
       </c>
       <c r="L13" t="n">
-        <v>1785000</v>
+        <v>3750</v>
       </c>
       <c r="M13" t="n">
-        <v>1735000</v>
+        <v>3460</v>
       </c>
       <c r="N13" t="n">
-        <v>50.2</v>
+        <v>3.11</v>
       </c>
       <c r="O13" t="n">
-        <v>1354719313500</v>
+        <v>4115677708</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>16110</v>
       </c>
       <c r="Q13" t="n">
-        <v>333000</v>
+        <v>2300</v>
       </c>
       <c r="R13" t="n">
-        <v>-172000</v>
+        <v>-276000</v>
       </c>
       <c r="S13" t="n">
-        <v>-24000</v>
+        <v>-9000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 금리 인상 불확실성 해소 및 미 증시 급등으로 인한 상승 기대감. 180~185 돌파 목표.</t>
+          <t>차익 실현 및 하락세 전망. 상장 폐지 및 폭락 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['금리인상', '미증시', '상승각']</t>
+          <t>['차익실현', '하락', '상장폐지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8370</v>
+        <v>8390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.12</v>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H14" t="n">
         <v>26.54</v>
@@ -1714,7 +1714,7 @@
         <v>26.66</v>
       </c>
       <c r="O14" t="n">
-        <v>5543672875</v>
+        <v>5831760630</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>중국 디스플레이 경쟁력 약화, 막대한 부채, 외인 연속 매도 등 부정적 요인으로 인한 하락 전망. 희망 없는 좀비 기업 평가.</t>
+          <t>중국 디스플레이 경쟁력 약화 및 높은 부채 비율, 연이은 하락세 속 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['중국', '부채', '외인매도']</t>
+          <t>['디스플레이', '중국', '악재']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13650</v>
+        <v>13620</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-2.51%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="H15" t="n">
         <v>0.01</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>9337992195</v>
+        <v>9655092575</v>
       </c>
       <c r="P15" t="n">
         <v>36200</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>겨울 대비 유가 상승 기대와 하락 전망이 혼재. 유가 변동성에 따른 주가 등락 예상.</t>
+          <t>유가 상승 및 외국인 매수세에 따른 주가 상승 기대감. 다만, 단기적인 유가 변동성과 전쟁 상황으로 인한 불확실성 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유가', '전망', '변동성']</t>
+          <t>['유가', '외국인', '전망']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20260917_10.xlsx
+++ b/data/trending_integrated_20260917_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>낮은 BPS와 시가총액, 지분 매수 공시 부재 속 상장폐지 우려 및 주가 하락에 대한 회의적인 시각.</t>
+          <t>지분 매수 공시 부재와 낮은 BPS로 인한 부정적 전망. 매수보다는 매도 의견.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['BPS', '상장폐지', '지분매수']</t>
+          <t>['BPS', '지분 매수', '상폐']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,27 +659,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22300</v>
+        <v>22750</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+31.56%</t>
+          <t>'+22.58%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="H3" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16950</v>
+        <v>18560</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>19260</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>22950</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>18920</v>
       </c>
       <c r="N3" t="n">
         <v>1.92</v>
       </c>
       <c r="O3" t="n">
-        <v>180474000000</v>
+        <v>194706144270</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>59600</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="R3" t="n">
         <v>-45000</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자회사 CPO 생산 장비 수주 및 광통신 섹터 대장주로서의 부각, 거래량 상위 기록.</t>
+          <t>자회사 CPO 생산 장비 수주 공시. 미장 광통신주 급등 및 데이터센터 관련 최대 수혜주로 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['CPO', '광통신', '수주']</t>
+          <t>['CPO', '수주', '광통신']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4130</v>
+        <v>4180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.55%</t>
+          <t>'+8.85%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F4" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G4" t="n">
-        <v>544</v>
+        <v>582</v>
       </c>
       <c r="H4" t="n">
         <v>0.95</v>
@@ -794,7 +794,7 @@
         <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>107623063405</v>
+        <v>112006900409</v>
       </c>
       <c r="P4" t="n">
         <v>6900</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오 인수 가능성 및 소프트뱅크 관련 호재로 인한 텐버거 기대감 속 물량 잠김 현상.</t>
+          <t>카카오 인수 및 소프트뱅크 관련 루머 확산. 텐버거 기대감 높은 상황.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['카카오', '인수', '텐버거']</t>
+          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10670</v>
+        <v>3785</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.02%</t>
+          <t>'+8.14%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.58</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="H5" t="n">
-        <v>1.25</v>
+        <v>8.01</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9970</v>
+        <v>3500</v>
       </c>
       <c r="K5" t="n">
-        <v>10280</v>
+        <v>3590</v>
       </c>
       <c r="L5" t="n">
-        <v>11750</v>
+        <v>4130</v>
       </c>
       <c r="M5" t="n">
-        <v>10250</v>
+        <v>3550</v>
       </c>
       <c r="N5" t="n">
-        <v>0.67</v>
+        <v>8.06</v>
       </c>
       <c r="O5" t="n">
-        <v>146316884275</v>
+        <v>59640622406</v>
       </c>
       <c r="P5" t="n">
-        <v>15960</v>
+        <v>19950</v>
       </c>
       <c r="Q5" t="n">
-        <v>3500</v>
+        <v>1913</v>
       </c>
       <c r="R5" t="n">
-        <v>350000</v>
+        <v>-1017000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료 관련 수혜 기대감 속 개인 투자자 매물 출회. 하지만 주가 상승 및 하락에 대한 엇갈린 전망.</t>
+          <t>우주 섹터 약세 및 주가 하락세 지속. 매집봉 출현 가능성 및 개인 매수 유도 경계.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '수혜주']</t>
+          <t>['우주섹터', '주가하락', '매집봉']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3705</v>
+        <v>10570</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.86%</t>
+          <t>'+6.02%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.58</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H6" t="n">
-        <v>8.01</v>
+        <v>1.25</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
+        <v>9970</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10280</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11750</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10250</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O6" t="n">
+        <v>148980098580</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3500</v>
       </c>
-      <c r="K6" t="n">
-        <v>3590</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4130</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3550</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="O6" t="n">
-        <v>53489863119</v>
-      </c>
-      <c r="P6" t="n">
-        <v>19950</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1913</v>
-      </c>
       <c r="R6" t="n">
-        <v>-1017000</v>
+        <v>350000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>프로그램 매도세 및 우주 섹터 약세 속 투자자들의 경계심 고조와 주가 하락 우려.</t>
+          <t>낙태약 및 탈모 치료제 관련 수혜 기대감. 그러나 외인 및 주포 이탈 정황 감지.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['우주섹터', '프로그램매도', '낙폭']</t>
+          <t>['낙태약', '탈모치료', '수혜주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21250</v>
+        <v>21350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.20%</t>
+          <t>'+5.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1061,7 +1061,7 @@
         <v>20450</v>
       </c>
       <c r="L7" t="n">
-        <v>21300</v>
+        <v>21350</v>
       </c>
       <c r="M7" t="n">
         <v>20450</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>23875744450</v>
+        <v>26752993025</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 중공업 업종 강세 속 목표주가 4만원 유지 리포트와 함께 주가 상승 기대감.</t>
+          <t>투자의견 '매수' 및 목표주가 4만원 제시. 조선업종 강세 속 상대적 저평가 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['중공업', '목표주가', '나스닥']</t>
+          <t>['투자의견', '목표주가', '조선업']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16510</v>
+        <v>16610</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.55%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2.93</v>
       </c>
       <c r="E8" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F8" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G8" t="n">
-        <v>752</v>
+        <v>796</v>
       </c>
       <c r="H8" t="n">
         <v>4.88</v>
@@ -1162,7 +1162,7 @@
         <v>1.95</v>
       </c>
       <c r="O8" t="n">
-        <v>217345702895</v>
+        <v>239533405325</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세에 따른 동반 상승 기대감 및 세계적 통신장비 부족 호재.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대. 세계적 통신장비 부족 이슈 및 2만원 목표 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85700</v>
+        <v>85900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="H9" t="n">
         <v>23.27</v>
@@ -1254,7 +1254,7 @@
         <v>23.37</v>
       </c>
       <c r="O9" t="n">
-        <v>53951128550</v>
+        <v>57082394700</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18690</v>
+        <v>18740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.65%</t>
+          <t>'+0.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.21</v>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="H10" t="n">
         <v>10.85</v>
@@ -1346,7 +1346,7 @@
         <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>26304216135</v>
+        <v>27320192155</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6천억 규모 수주 발표 및 대차 해지 운동 동참 독려. 금리 인상 우려 속 5만원 목표 기대감.</t>
+          <t>6천억 규모 수주 발표에도 주가 약세. 대차해지 운동 관련 논의 활발.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>255000</v>
+        <v>255250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'+0.69%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G11" t="n">
-        <v>2349</v>
+        <v>2257</v>
       </c>
       <c r="H11" t="n">
         <v>46.52</v>
@@ -1438,7 +1438,7 @@
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>784741260500</v>
+        <v>842743230250</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 금리 인상 우려 속에서 반도체 업황에 대한 단기적 긍정 전망 및 경계 혼재.</t>
+          <t>금리 인상 및 반도체 섹터 상승 모멘텀 강화. 정치적 이슈에 대한 언급 다수.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '메모리']</t>
+          <t>['금리인상', '반도체', '실적']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1759000</v>
+        <v>1760500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.09%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G12" t="n">
-        <v>1550</v>
+        <v>1485</v>
       </c>
       <c r="H12" t="n">
         <v>50.2</v>
@@ -1530,7 +1530,7 @@
         <v>50.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1508424079500</v>
+        <v>1597227391500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 증시 상승 및 악재 해소 기대감 속 자사주 매수 통한 주가 상승 전망.</t>
+          <t>미국 증시 반도체 섹터 상승 및 불확실성 해소에 따른 상승 기대감. ADR과의 괴리율 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주매수', '악재해소', '반도체']</t>
+          <t>['반도체', 'ADR', '자사주매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3515</v>
+        <v>3505</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.14%</t>
+          <t>'-0.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H13" t="n">
         <v>2.26</v>
@@ -1622,7 +1622,7 @@
         <v>3.11</v>
       </c>
       <c r="O13" t="n">
-        <v>4115677708</v>
+        <v>4222753133</v>
       </c>
       <c r="P13" t="n">
         <v>16110</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8390</v>
+        <v>8400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.12</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H14" t="n">
         <v>26.54</v>
@@ -1714,7 +1714,7 @@
         <v>26.66</v>
       </c>
       <c r="O14" t="n">
-        <v>5831760630</v>
+        <v>6011570735</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13620</v>
+        <v>13650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.51%</t>
+          <t>'-2.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F15" t="n">
         <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H15" t="n">
         <v>0.01</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>9655092575</v>
+        <v>9948929715</v>
       </c>
       <c r="P15" t="n">
         <v>36200</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>유가 상승 및 외국인 매수세에 따른 주가 상승 기대감. 다만, 단기적인 유가 변동성과 전쟁 상황으로 인한 불확실성 존재.</t>
+          <t>유가 등락에 따른 단기 등락 반복 예상. 외국인 대량 매수 언급 있으나 등락률은 소폭 하락.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유가', '외국인', '전망']</t>
+          <t>['유가', '외국인', '패턴']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1845,6 +1845,98 @@
       <c r="Z15" t="inlineStr">
         <is>
           <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4192</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-4.94%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E16" t="n">
+        <v>41</v>
+      </c>
+      <c r="F16" t="n">
+        <v>33</v>
+      </c>
+      <c r="G16" t="n">
+        <v>93</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>4410</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4415</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4420</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4120</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O16" t="n">
+        <v>30334812851</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>592</v>
+      </c>
+      <c r="R16" t="n">
+        <v>23000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>거래량 부진 및 투기과열종목 지정에 따른 주가 흐름 제한. 대한광통신 등 타 종목 대비 약세.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['투기과열', '거래량', '주가흐름']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>069540</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260917_10.xlsx
+++ b/data/trending_integrated_20260917_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+60.71%</t>
+          <t>'+32.14%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -610,7 +610,7 @@
         <v>3.71</v>
       </c>
       <c r="O2" t="n">
-        <v>186442216</v>
+        <v>252777740</v>
       </c>
       <c r="P2" t="n">
         <v>901</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>지분 매수 공시 부재와 낮은 BPS로 인한 부정적 전망. 매수보다는 매도 의견.</t>
+          <t>낮은 주가 및 희망고문 언급, 지분 매수 공시 부재로 인한 부정적 전망. 상폐 및 대주주 매수 관련 의혹 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['BPS', '지분 매수', '상폐']</t>
+          <t>['희망고문', '지분매수', '상폐']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,27 +659,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22750</v>
+        <v>22200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.58%</t>
+          <t>'+30.97%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H3" t="n">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>18560</v>
+        <v>16950</v>
       </c>
       <c r="K3" t="n">
-        <v>19260</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>22950</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>18920</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>1.92</v>
       </c>
       <c r="O3" t="n">
-        <v>194706144270</v>
+        <v>203167000000</v>
       </c>
       <c r="P3" t="n">
-        <v>59600</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>-45000</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자회사 CPO 생산 장비 수주 공시. 미장 광통신주 급등 및 데이터센터 관련 최대 수혜주로 부각.</t>
+          <t>자회사 ADST의 CPO 생산장비 1645만달러 규모 수주 공시. 광통신 테마 대장주로 부상하며 거래대금 1위 기록.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4180</v>
+        <v>4255</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.85%</t>
+          <t>'+10.81%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F4" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="H4" t="n">
         <v>0.95</v>
@@ -794,7 +794,7 @@
         <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>112006900409</v>
+        <v>121513344172</v>
       </c>
       <c r="P4" t="n">
         <v>6900</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오 인수 및 소프트뱅크 관련 루머 확산. 텐버거 기대감 높은 상황.</t>
+          <t>소프트뱅크 인수 및 카카오 관련 루머, 텐버거 가능성 언급으로 기대감 상승. 물량 잠김 및 흑자 기업으로 인한 상승 여력 강조.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
+          <t>['카카오인수', '텐버거', '소프트뱅크']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3785</v>
+        <v>3810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.14%</t>
+          <t>'+8.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
         <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H5" t="n">
         <v>8.01</v>
@@ -886,7 +886,7 @@
         <v>8.06</v>
       </c>
       <c r="O5" t="n">
-        <v>59640622406</v>
+        <v>63414172006</v>
       </c>
       <c r="P5" t="n">
         <v>19950</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10570</v>
+        <v>10690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.02%</t>
+          <t>'+7.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.58</v>
       </c>
       <c r="E6" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H6" t="n">
         <v>1.25</v>
@@ -978,7 +978,7 @@
         <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>148980098580</v>
+        <v>150726136480</v>
       </c>
       <c r="P6" t="n">
         <v>15960</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 수혜 기대감. 그러나 외인 및 주포 이탈 정황 감지.</t>
+          <t>낙태약 및 탈모 치료제 관련 수혜주로 언급되나, 개인 물량 이탈 및 주포 의혹 제기로 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '수혜주']</t>
+          <t>['낙태약', '탈모치료', '주포']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21350</v>
+        <v>21500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.69%</t>
+          <t>'+6.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1061,7 +1061,7 @@
         <v>20450</v>
       </c>
       <c r="L7" t="n">
-        <v>21350</v>
+        <v>21500</v>
       </c>
       <c r="M7" t="n">
         <v>20450</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>26752993025</v>
+        <v>30980765350</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>투자의견 '매수' 및 목표주가 4만원 제시. 조선업종 강세 속 상대적 저평가 논의.</t>
+          <t>나스닥 반등 및 금리 인상에도 불구하고 투자의견 '매수'와 목표주가 4만원 유지. 주포 변경 시 생존 가능성 및 자사주 소각 공시 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['투자의견', '목표주가', '조선업']</t>
+          <t>['투자의견', '목표주가', '자사주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,79 +1115,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16610</v>
+        <v>86000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.17%</t>
+          <t>'+2.63%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.93</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F8" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>796</v>
+        <v>510</v>
       </c>
       <c r="H8" t="n">
-        <v>4.88</v>
+        <v>23.27</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16100</v>
+        <v>83800</v>
       </c>
       <c r="K8" t="n">
-        <v>16200</v>
+        <v>84700</v>
       </c>
       <c r="L8" t="n">
-        <v>16750</v>
+        <v>86000</v>
       </c>
       <c r="M8" t="n">
-        <v>15560</v>
+        <v>84100</v>
       </c>
       <c r="N8" t="n">
-        <v>1.95</v>
+        <v>23.37</v>
       </c>
       <c r="O8" t="n">
-        <v>239533405325</v>
+        <v>60225973550</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>-173000</v>
+        <v>-75000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 수혜 기대. 세계적 통신장비 부족 이슈 및 2만원 목표 제시.</t>
+          <t>AI 투자 대비 전력 부족 가능성 제기. FOMC 악재 소멸 및 금리 인상 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '통신장비', '호재']</t>
+          <t>['AI', '금리 인상', '원전']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85900</v>
+        <v>16490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+2.42%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1</v>
+        <v>2.93</v>
       </c>
       <c r="E9" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G9" t="n">
-        <v>505</v>
+        <v>809</v>
       </c>
       <c r="H9" t="n">
-        <v>23.27</v>
+        <v>4.88</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>83800</v>
+        <v>16100</v>
       </c>
       <c r="K9" t="n">
-        <v>84700</v>
+        <v>16200</v>
       </c>
       <c r="L9" t="n">
-        <v>86000</v>
+        <v>16750</v>
       </c>
       <c r="M9" t="n">
-        <v>84100</v>
+        <v>15560</v>
       </c>
       <c r="N9" t="n">
-        <v>23.37</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>57082394700</v>
+        <v>252843906960</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R9" t="n">
-        <v>-75000</v>
+        <v>-173000</v>
       </c>
       <c r="S9" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 투자 대비 전력 부족 가능성 제기. FOMC 악재 소멸 및 금리 인상 관련 언급.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대. 세계적 통신장비 부족 이슈 및 2만원 목표 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '금리 인상', '원전']</t>
+          <t>['광통신', '통신장비', '호재']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>0.21</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="H10" t="n">
         <v>10.85</v>
@@ -1346,7 +1346,7 @@
         <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>27320192155</v>
+        <v>28355757790</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>255250</v>
+        <v>254500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.69%</t>
+          <t>'+0.39%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="G11" t="n">
-        <v>2257</v>
+        <v>2181</v>
       </c>
       <c r="H11" t="n">
         <v>46.52</v>
@@ -1438,7 +1438,7 @@
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>842743230250</v>
+        <v>898386279750</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>금리 인상 및 반도체 섹터 상승 모멘텀 강화. 정치적 이슈에 대한 언급 다수.</t>
+          <t>정치적 이슈와 함께 반도체 섹터 상승 모멘텀 분석. 금리 인상 불확실성 해소 및 엔비디아, 마이크론 상승세 연동 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '실적']</t>
+          <t>['반도체', '금리인상', '모멘텀']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1760500</v>
+        <v>1752000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.09%</t>
+          <t>'-0.40%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>454</v>
       </c>
       <c r="G12" t="n">
-        <v>1485</v>
+        <v>1507</v>
       </c>
       <c r="H12" t="n">
         <v>50.2</v>
@@ -1530,7 +1530,7 @@
         <v>50.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1597227391500</v>
+        <v>1676310817000</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 섹터 상승 및 불확실성 해소에 따른 상승 기대감. ADR과의 괴리율 언급.</t>
+          <t>미국 증시 상승 및 불확실성 해소로 인한 자사주 매수 통한 상승 기대감. 180 돌파 및 상승 여력 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', 'ADR', '자사주매수']</t>
+          <t>['자사주매수', '상승각', '괴리율']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,70 +1575,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3505</v>
+        <v>10390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.43%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.85</v>
+        <v>-0.8</v>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>210</v>
+        <v>94</v>
       </c>
       <c r="H13" t="n">
-        <v>2.26</v>
+        <v>18.42</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3520</v>
+        <v>10460</v>
       </c>
       <c r="K13" t="n">
-        <v>3730</v>
+        <v>10860</v>
       </c>
       <c r="L13" t="n">
-        <v>3750</v>
+        <v>11150</v>
       </c>
       <c r="M13" t="n">
-        <v>3460</v>
+        <v>10080</v>
       </c>
       <c r="N13" t="n">
-        <v>3.11</v>
+        <v>19.22</v>
       </c>
       <c r="O13" t="n">
-        <v>4222753133</v>
+        <v>46240791735</v>
       </c>
       <c r="P13" t="n">
-        <v>16110</v>
+        <v>22450</v>
       </c>
       <c r="Q13" t="n">
-        <v>2300</v>
+        <v>1760</v>
       </c>
       <c r="R13" t="n">
-        <v>-276000</v>
+        <v>-39000</v>
       </c>
       <c r="S13" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>차익 실현 및 하락세 전망. 상장 폐지 및 폭락 가능성 언급.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['차익실현', '하락', '상장폐지']</t>
+          <t>['주포', '시총', '횡보']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8400</v>
+        <v>3495</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.71%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.12</v>
+        <v>-0.85</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="H14" t="n">
-        <v>26.54</v>
+        <v>2.26</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8470</v>
+        <v>3520</v>
       </c>
       <c r="K14" t="n">
-        <v>8470</v>
+        <v>3730</v>
       </c>
       <c r="L14" t="n">
-        <v>8510</v>
+        <v>3750</v>
       </c>
       <c r="M14" t="n">
-        <v>8360</v>
+        <v>3460</v>
       </c>
       <c r="N14" t="n">
-        <v>26.66</v>
+        <v>3.11</v>
       </c>
       <c r="O14" t="n">
-        <v>6011570735</v>
+        <v>4353920304</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>16110</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>2300</v>
       </c>
       <c r="R14" t="n">
-        <v>-169000</v>
+        <v>-276000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>중국 디스플레이 경쟁력 약화 및 높은 부채 비율, 연이은 하락세 속 투자 심리 위축.</t>
+          <t>명확한 근거 없는 하락 및 상폐 우려, 주주들의 부정적 심리 확산.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['디스플레이', '중국', '악재']</t>
+          <t>['하락', '상폐', '불확실성']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13650</v>
+        <v>8400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01</v>
+        <v>26.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13970</v>
+        <v>8470</v>
       </c>
       <c r="K15" t="n">
-        <v>13450</v>
+        <v>8470</v>
       </c>
       <c r="L15" t="n">
-        <v>13970</v>
+        <v>8510</v>
       </c>
       <c r="M15" t="n">
-        <v>13410</v>
+        <v>8360</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>9948929715</v>
+        <v>6379383860</v>
       </c>
       <c r="P15" t="n">
-        <v>36200</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>8920</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>116000</v>
+        <v>-169000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>유가 등락에 따른 단기 등락 반복 예상. 외국인 대량 매수 언급 있으나 등락률은 소폭 하락.</t>
+          <t>중국 디스플레이 산업 경쟁력 약화 및 막대한 부채, 연속 하락세로 부정적 전망. 무능한 경영진 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유가', '외국인', '패턴']</t>
+          <t>['디스플레이', '부채', '악재']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4192</v>
+        <v>13810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.94%</t>
+          <t>'-1.15%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>93</v>
+        <v>246</v>
       </c>
       <c r="H16" t="n">
-        <v>0.87</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4410</v>
+        <v>13970</v>
       </c>
       <c r="K16" t="n">
-        <v>4415</v>
+        <v>13450</v>
       </c>
       <c r="L16" t="n">
-        <v>4420</v>
+        <v>13970</v>
       </c>
       <c r="M16" t="n">
-        <v>4120</v>
+        <v>13410</v>
       </c>
       <c r="N16" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>30334812851</v>
+        <v>10331474885</v>
       </c>
       <c r="P16" t="n">
-        <v>8100</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>592</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>23000</v>
+        <v>116000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>거래량 부진 및 투기과열종목 지정에 따른 주가 흐름 제한. 대한광통신 등 타 종목 대비 약세.</t>
+          <t>유가 변동성에 따른 단기 등락 전망. 외국인 대량 매수 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,18 +1923,110 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['투기과열', '거래량', '주가흐름']</t>
+          <t>['유가', '외국인', '변동성']</t>
         </is>
       </c>
       <c r="X16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4205</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-4.65%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E17" t="n">
+        <v>42</v>
+      </c>
+      <c r="F17" t="n">
+        <v>34</v>
+      </c>
+      <c r="G17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4410</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4415</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4420</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4120</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O17" t="n">
+        <v>31262593767</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>592</v>
+      </c>
+      <c r="R17" t="n">
+        <v>23000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>미국 광통신 테마 급등과 연관되어 상승 기대감 있으나, 연이은 투경(거래정지)으로 인한 변동성 및 매도 심리.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['광통신', '투경', '급등']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
         <v>8</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>069540</t>
         </is>

--- a/data/trending_integrated_20260917_10.xlsx
+++ b/data/trending_integrated_20260917_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
         <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>낮은 주가 및 희망고문 언급, 지분 매수 공시 부재로 인한 부정적 전망. 상폐 및 대주주 매수 관련 의혹 제기.</t>
+          <t>주가 부양 의지 부족 및 관리 종목 지정 가능성에 대한 우려. 주가 하락 및 상장폐지 관련 부정적 논의.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['희망고문', '지분매수', '상폐']</t>
+          <t>['관리종목', '상폐', '지분매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22200</v>
+        <v>1669</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+30.97%</t>
+          <t>'+19.47%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="H3" t="n">
-        <v>2.61</v>
+        <v>3.52</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16950</v>
+        <v>1397</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1395</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1369</v>
       </c>
       <c r="N3" t="n">
-        <v>1.92</v>
+        <v>3.57</v>
       </c>
       <c r="O3" t="n">
-        <v>203167000000</v>
+        <v>35849339721</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5140</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="R3" t="n">
-        <v>-45000</v>
+        <v>222000</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>-7000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자회사 ADST의 CPO 생산장비 1645만달러 규모 수주 공시. 광통신 테마 대장주로 부상하며 거래대금 1위 기록.</t>
+          <t>유증 성공 및 우주, 방산, 통신주 테마 편입 기대감. 스페이스X 관련주로 부각되며 주가 상승 논의.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['CPO', '수주', '광통신']</t>
+          <t>['유상증자', '우주', '스페이스X']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>321370</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4255</v>
+        <v>21900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.81%</t>
+          <t>'+18.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>231</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>594</v>
+        <v>140</v>
       </c>
       <c r="H4" t="n">
-        <v>0.95</v>
+        <v>2.54</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3840</v>
+        <v>18560</v>
       </c>
       <c r="K4" t="n">
-        <v>4170</v>
+        <v>19260</v>
       </c>
       <c r="L4" t="n">
-        <v>4500</v>
+        <v>22950</v>
       </c>
       <c r="M4" t="n">
-        <v>3990</v>
+        <v>18920</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>121513344172</v>
+        <v>213436765420</v>
       </c>
       <c r="P4" t="n">
-        <v>6900</v>
+        <v>59600</v>
       </c>
       <c r="Q4" t="n">
-        <v>1738</v>
+        <v>1030</v>
       </c>
       <c r="R4" t="n">
-        <v>101000</v>
+        <v>-45000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>소프트뱅크 인수 및 카카오 관련 루머, 텐버거 가능성 언급으로 기대감 상승. 물량 잠김 및 흑자 기업으로 인한 상승 여력 강조.</t>
+          <t>자회사 CPO 생산 장비 수주 확정 및 미국 광통신주 급등에 따른 광통신 테마 대장주 부각. 데이터센터 관련 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['카카오인수', '텐버거', '소프트뱅크']</t>
+          <t>['CPO', '수주', '광통신']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3810</v>
+        <v>4290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.86%</t>
+          <t>'+11.72%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>243</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="G5" t="n">
-        <v>138</v>
+        <v>601</v>
       </c>
       <c r="H5" t="n">
-        <v>8.01</v>
+        <v>0.95</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3500</v>
+        <v>3840</v>
       </c>
       <c r="K5" t="n">
-        <v>3590</v>
+        <v>4170</v>
       </c>
       <c r="L5" t="n">
-        <v>4130</v>
+        <v>4500</v>
       </c>
       <c r="M5" t="n">
-        <v>3550</v>
+        <v>3990</v>
       </c>
       <c r="N5" t="n">
-        <v>8.06</v>
+        <v>1.03</v>
       </c>
       <c r="O5" t="n">
-        <v>63414172006</v>
+        <v>128166225885</v>
       </c>
       <c r="P5" t="n">
-        <v>19950</v>
+        <v>6900</v>
       </c>
       <c r="Q5" t="n">
-        <v>1913</v>
+        <v>1738</v>
       </c>
       <c r="R5" t="n">
-        <v>-1017000</v>
+        <v>101000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>우주 섹터 약세 및 주가 하락세 지속. 매집봉 출현 가능성 및 개인 매수 유도 경계.</t>
+          <t>카카오 인수 및 소프트뱅크 관련 루머 확산. 텐버거 기대감 높은 상황.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가하락', '매집봉']</t>
+          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10690</v>
+        <v>10790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.22%</t>
+          <t>'+8.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.58</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H6" t="n">
         <v>1.25</v>
@@ -978,7 +978,7 @@
         <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>150726136480</v>
+        <v>155897953885</v>
       </c>
       <c r="P6" t="n">
         <v>15960</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 수혜주로 언급되나, 개인 물량 이탈 및 주포 의혹 제기로 투자 심리 위축.</t>
+          <t>낙태약 도입 및 탈모 치료 관련 수혜주 기대감 속 개인 매도 및 외국인 이탈 발생. 주가 상승 기대감과 매도 압력이 공존.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '주포']</t>
+          <t>['낙태약', '탈모치료', '수혜주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21500</v>
+        <v>3765</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.44%</t>
+          <t>'+7.57%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
         <v>142</v>
       </c>
       <c r="H7" t="n">
-        <v>28.36</v>
+        <v>8.01</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>20200</v>
+        <v>3500</v>
       </c>
       <c r="K7" t="n">
-        <v>20450</v>
+        <v>3590</v>
       </c>
       <c r="L7" t="n">
-        <v>21500</v>
+        <v>4130</v>
       </c>
       <c r="M7" t="n">
-        <v>20450</v>
+        <v>3550</v>
       </c>
       <c r="N7" t="n">
-        <v>28.51</v>
+        <v>8.06</v>
       </c>
       <c r="O7" t="n">
-        <v>30980765350</v>
+        <v>64886762061</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>19950</v>
       </c>
       <c r="Q7" t="n">
-        <v>18440</v>
+        <v>1913</v>
       </c>
       <c r="R7" t="n">
-        <v>400000</v>
+        <v>-1017000</v>
       </c>
       <c r="S7" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 금리 인상에도 불구하고 투자의견 '매수'와 목표주가 4만원 유지. 주포 변경 시 생존 가능성 및 자사주 소각 공시 기대.</t>
+          <t>우주 섹터 약세 및 주가 하락세 지속. 매집봉 출현 가능성 및 개인 매수 유도 경계.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['투자의견', '목표주가', '자사주']</t>
+          <t>['우주섹터', '주가하락', '매집봉']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86000</v>
+        <v>21600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.63%</t>
+          <t>'+6.93%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>510</v>
+        <v>173</v>
       </c>
       <c r="H8" t="n">
-        <v>23.27</v>
+        <v>28.36</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>83800</v>
+        <v>20200</v>
       </c>
       <c r="K8" t="n">
-        <v>84700</v>
+        <v>20450</v>
       </c>
       <c r="L8" t="n">
-        <v>86000</v>
+        <v>21650</v>
       </c>
       <c r="M8" t="n">
-        <v>84100</v>
+        <v>20450</v>
       </c>
       <c r="N8" t="n">
-        <v>23.37</v>
+        <v>28.51</v>
       </c>
       <c r="O8" t="n">
-        <v>60225973550</v>
+        <v>37308390750</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>18440</v>
       </c>
       <c r="R8" t="n">
-        <v>-75000</v>
+        <v>400000</v>
       </c>
       <c r="S8" t="n">
-        <v>-18000</v>
+        <v>15000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 투자 대비 전력 부족 가능성 제기. FOMC 악재 소멸 및 금리 인상 관련 언급.</t>
+          <t>나스닥 반등 및 금리 인상 우려 속에서 매수 의견 및 목표가 4만원 유지. 주가 부양 필요성과 변동성 논의.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '금리 인상', '원전']</t>
+          <t>['부유식', '목표주가', '자사주소각']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16490</v>
+        <v>13690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.42%</t>
+          <t>'+5.96%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.93</v>
+        <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>809</v>
+        <v>228</v>
       </c>
       <c r="H9" t="n">
-        <v>4.88</v>
+        <v>4.99</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>16100</v>
+        <v>12920</v>
       </c>
       <c r="K9" t="n">
-        <v>16200</v>
+        <v>12920</v>
       </c>
       <c r="L9" t="n">
-        <v>16750</v>
+        <v>13770</v>
       </c>
       <c r="M9" t="n">
-        <v>15560</v>
+        <v>12910</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>252843906960</v>
+        <v>37399140050</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>3540</v>
       </c>
       <c r="R9" t="n">
-        <v>-173000</v>
+        <v>-80000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 수혜 기대. 세계적 통신장비 부족 이슈 및 2만원 목표 제시.</t>
+          <t>신한울 3,4호기 DCS 계약 체결 소식과 9월 23일 대미 투자 발표 기대감. 해외 원전 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '통신장비', '호재']</t>
+          <t>['DCS 계약', '해외 원전', '대미 투자']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18740</v>
+        <v>86500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.92%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.21</v>
+        <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>228</v>
+        <v>519</v>
       </c>
       <c r="H10" t="n">
-        <v>10.85</v>
+        <v>23.27</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18570</v>
+        <v>83800</v>
       </c>
       <c r="K10" t="n">
-        <v>18740</v>
+        <v>84700</v>
       </c>
       <c r="L10" t="n">
-        <v>18900</v>
+        <v>86600</v>
       </c>
       <c r="M10" t="n">
-        <v>18580</v>
+        <v>84100</v>
       </c>
       <c r="N10" t="n">
-        <v>10.64</v>
+        <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>28355757790</v>
+        <v>66773573800</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-143000</v>
+        <v>-75000</v>
       </c>
       <c r="S10" t="n">
-        <v>-20000</v>
+        <v>-18000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6천억 규모 수주 발표에도 주가 약세. 대차해지 운동 관련 논의 활발.</t>
+          <t>미 금리 인상 및 대미 투자 관련 논의. AP1000 관련 추정치 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '대차해지', '금리인상']</t>
+          <t>['금리 인상', '대미 투자', 'AP1000']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254500</v>
+        <v>18870</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.39%</t>
+          <t>'+1.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>425</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>2181</v>
+        <v>231</v>
       </c>
       <c r="H11" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>253500</v>
+        <v>18570</v>
       </c>
       <c r="K11" t="n">
-        <v>257000</v>
+        <v>18740</v>
       </c>
       <c r="L11" t="n">
-        <v>259000</v>
+        <v>18900</v>
       </c>
       <c r="M11" t="n">
-        <v>252000</v>
+        <v>18580</v>
       </c>
       <c r="N11" t="n">
-        <v>46.56</v>
+        <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>898386279750</v>
+        <v>30769467495</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>77100</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-149000</v>
+        <v>-143000</v>
       </c>
       <c r="S11" t="n">
-        <v>-85000</v>
+        <v>-20000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 반도체 섹터 상승 모멘텀 분석. 금리 인상 불확실성 해소 및 엔비디아, 마이크론 상승세 연동 가능성 언급.</t>
+          <t>6천억 규모 수주 발표에도 주가 약세. 대차해지 운동 관련 논의 활발.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '금리인상', '모멘텀']</t>
+          <t>['수주', '대차해지', '금리인상']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1752000</v>
+        <v>16360</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.40%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E12" t="n">
+        <v>183</v>
+      </c>
+      <c r="F12" t="n">
+        <v>105</v>
+      </c>
+      <c r="G12" t="n">
+        <v>854</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>16100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>16200</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16750</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15560</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O12" t="n">
+        <v>261411882000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-173000</v>
+      </c>
+      <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>800</v>
-      </c>
-      <c r="F12" t="n">
-        <v>454</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1507</v>
-      </c>
-      <c r="H12" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1759000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1770000</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1785000</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1735000</v>
-      </c>
-      <c r="N12" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1676310817000</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2987000</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>333000</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-172000</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-24000</v>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 증시 상승 및 불확실성 해소로 인한 자사주 매수 통한 상승 기대감. 180 돌파 및 상승 여력 언급.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대감. 통신장비 부족 현상과 2만원 목표 주가 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주매수', '상승각', '괴리율']</t>
+          <t>['광통신', '통신장비', '미국주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10390</v>
+        <v>254500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'+0.39%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.8</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>434</v>
       </c>
       <c r="G13" t="n">
-        <v>94</v>
+        <v>2208</v>
       </c>
       <c r="H13" t="n">
-        <v>18.42</v>
+        <v>46.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10460</v>
+        <v>253500</v>
       </c>
       <c r="K13" t="n">
-        <v>10860</v>
+        <v>257000</v>
       </c>
       <c r="L13" t="n">
-        <v>11150</v>
+        <v>259000</v>
       </c>
       <c r="M13" t="n">
-        <v>10080</v>
+        <v>252000</v>
       </c>
       <c r="N13" t="n">
-        <v>19.22</v>
+        <v>46.56</v>
       </c>
       <c r="O13" t="n">
-        <v>46240791735</v>
+        <v>951225184000</v>
       </c>
       <c r="P13" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>1760</v>
+        <v>77100</v>
       </c>
       <c r="R13" t="n">
-        <v>-39000</v>
+        <v>-149000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-85000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>정치적 이슈와 함께 반도체 섹터 상승 모멘텀 분석. 금리 인상 불확실성 해소 및 엔비디아, 마이크론 상승세 연동 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['반도체', '금리인상', '모멘텀']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3495</v>
+        <v>13580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.71%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.85</v>
+        <v>1.36</v>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G14" t="n">
-        <v>226</v>
+        <v>68</v>
       </c>
       <c r="H14" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3520</v>
+        <v>13530</v>
       </c>
       <c r="K14" t="n">
-        <v>3730</v>
+        <v>14280</v>
       </c>
       <c r="L14" t="n">
-        <v>3750</v>
+        <v>14800</v>
       </c>
       <c r="M14" t="n">
-        <v>3460</v>
+        <v>13130</v>
       </c>
       <c r="N14" t="n">
-        <v>3.11</v>
+        <v>0.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4353920304</v>
+        <v>71242766990</v>
       </c>
       <c r="P14" t="n">
-        <v>16110</v>
+        <v>25700</v>
       </c>
       <c r="Q14" t="n">
-        <v>2300</v>
+        <v>4600</v>
       </c>
       <c r="R14" t="n">
-        <v>-276000</v>
+        <v>2000</v>
       </c>
       <c r="S14" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>명확한 근거 없는 하락 및 상폐 우려, 주주들의 부정적 심리 확산.</t>
+          <t>미국 광통신주 급등으로 인한 기대감 형성. 일부 긍정적 전망과 함께 주가 부양 의지 및 상승 여력에 대한 논의.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['하락', '상폐', '불확실성']</t>
+          <t>['광통신', '미국주가', '목표가']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8400</v>
+        <v>1755000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>460</v>
       </c>
       <c r="G15" t="n">
-        <v>181</v>
+        <v>1477</v>
       </c>
       <c r="H15" t="n">
-        <v>26.54</v>
+        <v>50.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8470</v>
+        <v>1759000</v>
       </c>
       <c r="K15" t="n">
-        <v>8470</v>
+        <v>1770000</v>
       </c>
       <c r="L15" t="n">
-        <v>8510</v>
+        <v>1785000</v>
       </c>
       <c r="M15" t="n">
-        <v>8360</v>
+        <v>1735000</v>
       </c>
       <c r="N15" t="n">
-        <v>26.66</v>
+        <v>50.2</v>
       </c>
       <c r="O15" t="n">
-        <v>6379383860</v>
+        <v>1763426452000</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R15" t="n">
-        <v>-169000</v>
+        <v>-172000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>중국 디스플레이 산업 경쟁력 약화 및 막대한 부채, 연속 하락세로 부정적 전망. 무능한 경영진 비판.</t>
+          <t>ADR 괴리율 해소 및 자사주 매수 기대감으로 인한 상승 전망. 악재 소멸 후 상승각 논의.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['디스플레이', '부채', '악재']</t>
+          <t>['ADR', '괴리율', '자사주매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13810</v>
+        <v>8450</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.15%</t>
+          <t>'-0.24%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>26.54</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13970</v>
+        <v>8470</v>
       </c>
       <c r="K16" t="n">
-        <v>13450</v>
+        <v>8470</v>
       </c>
       <c r="L16" t="n">
-        <v>13970</v>
+        <v>8510</v>
       </c>
       <c r="M16" t="n">
-        <v>13410</v>
+        <v>8360</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>26.66</v>
       </c>
       <c r="O16" t="n">
-        <v>10331474885</v>
+        <v>7187819275</v>
       </c>
       <c r="P16" t="n">
-        <v>36200</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>8920</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>116000</v>
+        <v>-169000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 변동성에 따른 단기 등락 전망. 외국인 대량 매수 확인.</t>
+          <t>중국 디스플레이 산업에 대한 경쟁력 약화 및 높은 부채 비율로 인한 부정적 전망. 경영 능력 의문 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유가', '외국인', '변동성']</t>
+          <t>['중국', '영업이익', '부채']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4205</v>
+        <v>3490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.65%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.13</v>
+        <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="H17" t="n">
-        <v>0.87</v>
+        <v>2.26</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,58 +1975,334 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4410</v>
+        <v>3520</v>
       </c>
       <c r="K17" t="n">
-        <v>4415</v>
+        <v>3730</v>
       </c>
       <c r="L17" t="n">
-        <v>4420</v>
+        <v>3750</v>
       </c>
       <c r="M17" t="n">
-        <v>4120</v>
+        <v>3460</v>
       </c>
       <c r="N17" t="n">
-        <v>0.74</v>
+        <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>31262593767</v>
+        <v>4451141577</v>
       </c>
       <c r="P17" t="n">
-        <v>8100</v>
+        <v>16110</v>
       </c>
       <c r="Q17" t="n">
-        <v>592</v>
+        <v>2300</v>
       </c>
       <c r="R17" t="n">
-        <v>23000</v>
+        <v>-276000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신 테마 급등과 연관되어 상승 기대감 있으나, 연이은 투경(거래정지)으로 인한 변동성 및 매도 심리.</t>
+          <t>명확한 근거 없는 하락 및 상폐 우려, 주주들의 부정적 심리 확산.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['하락', '상폐', '불확실성']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>424870</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>13790</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-1.29%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" t="n">
+        <v>91</v>
+      </c>
+      <c r="F18" t="n">
+        <v>57</v>
+      </c>
+      <c r="G18" t="n">
+        <v>253</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>13970</v>
+      </c>
+      <c r="K18" t="n">
+        <v>13450</v>
+      </c>
+      <c r="L18" t="n">
+        <v>13970</v>
+      </c>
+      <c r="M18" t="n">
+        <v>13410</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10676287705</v>
+      </c>
+      <c r="P18" t="n">
+        <v>36200</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8920</v>
+      </c>
+      <c r="R18" t="n">
+        <v>116000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>국제 유가 변동성에 따른 단기적 등락 전망. 유가 조정 시 상승, 폭등 시 하락 패턴 반복 예상.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
         <v>0.2</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>['광통신', '투경', '급등']</t>
-        </is>
-      </c>
-      <c r="X17" t="n">
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['국제 유가', '유가 변동성', '등락 패턴']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10290</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-1.63%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>43</v>
+      </c>
+      <c r="F19" t="n">
+        <v>32</v>
+      </c>
+      <c r="G19" t="n">
+        <v>94</v>
+      </c>
+      <c r="H19" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>10460</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10860</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11150</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10080</v>
+      </c>
+      <c r="N19" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="O19" t="n">
+        <v>46935321105</v>
+      </c>
+      <c r="P19" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-39000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['주포', '시총', '횡보']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>017900</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4190</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-4.99%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41</v>
+      </c>
+      <c r="F20" t="n">
+        <v>32</v>
+      </c>
+      <c r="G20" t="n">
+        <v>96</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>4410</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4415</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4420</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4120</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O20" t="n">
+        <v>32147701440</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>592</v>
+      </c>
+      <c r="R20" t="n">
+        <v>23000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>투기 과열 종목 지정으로 인한 주가 변동성 및 매도 압력 발생. 광통신 테마 내에서 대한광통신 대비 약세 언급.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['투기과열', '광통신', '주가변동']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
         <v>8</v>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>069540</t>
         </is>

--- a/data/trending_integrated_20260917_10.xlsx
+++ b/data/trending_integrated_20260917_10.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>주가 부양 의지 부족 및 관리 종목 지정 가능성에 대한 우려. 주가 하락 및 상장폐지 관련 부정적 논의.</t>
+          <t>주가 하락 및 낮은 가격대에서의 희망고문 지속. 지분 매수 공시 부재와 낮은 BPS.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['관리종목', '상폐', '지분매수']</t>
+          <t>['희망고문', '지분매수', 'BPS']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1669</v>
+        <v>1663</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.47%</t>
+          <t>'+19.04%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
         <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" t="n">
         <v>3.52</v>
@@ -702,7 +702,7 @@
         <v>3.57</v>
       </c>
       <c r="O3" t="n">
-        <v>35849339721</v>
+        <v>36990615992</v>
       </c>
       <c r="P3" t="n">
         <v>5140</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>유증 성공 및 우주, 방산, 통신주 테마 편입 기대감. 스페이스X 관련주로 부각되며 주가 상승 논의.</t>
+          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유상증자', '우주', '스페이스X']</t>
+          <t>['우주', '스페이스X', '유상증자']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21900</v>
+        <v>21625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.00%</t>
+          <t>'+16.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="H4" t="n">
         <v>2.54</v>
@@ -794,7 +794,7 @@
         <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>213436765420</v>
+        <v>226786695345</v>
       </c>
       <c r="P4" t="n">
         <v>59600</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자회사 CPO 생산 장비 수주 확정 및 미국 광통신주 급등에 따른 광통신 테마 대장주 부각. 데이터센터 관련 기대감.</t>
+          <t>자회사 CPO 생산 장비 수주 및 광통신 섹터 대장주 부각. 루멘텀 급등.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['CPO', '수주', '광통신']</t>
+          <t>['CPO', '광통신', '수주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4290</v>
+        <v>4270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.72%</t>
+          <t>'+11.20%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G5" t="n">
-        <v>601</v>
+        <v>624</v>
       </c>
       <c r="H5" t="n">
         <v>0.95</v>
@@ -886,7 +886,7 @@
         <v>1.03</v>
       </c>
       <c r="O5" t="n">
-        <v>128166225885</v>
+        <v>132599623132</v>
       </c>
       <c r="P5" t="n">
         <v>6900</v>
@@ -902,12 +902,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>카카오 인수 및 소프트뱅크 관련 루머 확산. 텐버거 기대감 높은 상황.</t>
+          <t>카카오 인수 및 소프트뱅크 관련 텐버거 기대감. 흑자기업 PBR 1 이하 저평가 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10790</v>
+        <v>3780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.22%</t>
+          <t>'+8.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.58</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H6" t="n">
-        <v>1.25</v>
+        <v>8.01</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9970</v>
+        <v>3500</v>
       </c>
       <c r="K6" t="n">
-        <v>10280</v>
+        <v>3590</v>
       </c>
       <c r="L6" t="n">
-        <v>11750</v>
+        <v>4130</v>
       </c>
       <c r="M6" t="n">
-        <v>10250</v>
+        <v>3550</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>155897953885</v>
+        <v>65722924779</v>
       </c>
       <c r="P6" t="n">
-        <v>15960</v>
+        <v>19950</v>
       </c>
       <c r="Q6" t="n">
-        <v>3500</v>
+        <v>1913</v>
       </c>
       <c r="R6" t="n">
-        <v>350000</v>
+        <v>-1017000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>낙태약 도입 및 탈모 치료 관련 수혜주 기대감 속 개인 매도 및 외국인 이탈 발생. 주가 상승 기대감과 매도 압력이 공존.</t>
+          <t>스페이스 이슈에도 불구하고 주가 하락 우려. 매수 시 추가 하락 가능성 경고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '수혜주']</t>
+          <t>['스페이스', '주가하락', '매수주의']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3765</v>
+        <v>10700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.57%</t>
+          <t>'+7.32%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0.58</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H7" t="n">
-        <v>8.01</v>
+        <v>1.25</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
+        <v>9970</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10280</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11750</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10250</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O7" t="n">
+        <v>157846222475</v>
+      </c>
+      <c r="P7" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3500</v>
       </c>
-      <c r="K7" t="n">
-        <v>3590</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4130</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3550</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="O7" t="n">
-        <v>64886762061</v>
-      </c>
-      <c r="P7" t="n">
-        <v>19950</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1913</v>
-      </c>
       <c r="R7" t="n">
-        <v>-1017000</v>
+        <v>350000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>우주 섹터 약세 및 주가 하락세 지속. 매집봉 출현 가능성 및 개인 매수 유도 경계.</t>
+          <t>낙태약 및 탈모 치료 관련 수혜 기대감. 외인 및 주포 이탈 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가하락', '매집봉']</t>
+          <t>['낙태약', '탈모치료', '수혜주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-0.15</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="H8" t="n">
         <v>28.36</v>
@@ -1153,7 +1153,7 @@
         <v>20450</v>
       </c>
       <c r="L8" t="n">
-        <v>21650</v>
+        <v>21750</v>
       </c>
       <c r="M8" t="n">
         <v>20450</v>
@@ -1162,7 +1162,7 @@
         <v>28.51</v>
       </c>
       <c r="O8" t="n">
-        <v>37308390750</v>
+        <v>42191884700</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 금리 인상 우려 속에서 매수 의견 및 목표가 4만원 유지. 주가 부양 필요성과 변동성 논의.</t>
+          <t>나스닥 반등 및 금리 인상에도 불구하고 긍정적 전망. 투자의견 '매수' 유지.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['부유식', '목표주가', '자사주소각']</t>
+          <t>['나스닥', '금리인상', '투자의견']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13690</v>
+        <v>13540</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.96%</t>
+          <t>'+4.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>37399140050</v>
+        <v>40708836865</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신한울 3,4호기 DCS 계약 체결 소식과 9월 23일 대미 투자 발표 기대감. 해외 원전 관련 긍정적 전망.</t>
+          <t>신한울 3.4호기 DCS 계약 체결 공시 기반 상승 기대감. 해외 원전 관련 우상향 추세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['DCS 계약', '해외 원전', '대미 투자']</t>
+          <t>['DCS계약', '원전', '추세']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86500</v>
+        <v>86200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+2.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>66773573800</v>
+        <v>71365657100</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미 금리 인상 및 대미 투자 관련 논의. AP1000 관련 추정치 언급.</t>
+          <t>FOMC 악재 통과 및 대미 원전 투자 관련 긍정적 전망. 금리 인상 관련 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['금리 인상', '대미 투자', 'AP1000']</t>
+          <t>['원전', '금리인상', 'FOMC']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18870</v>
+        <v>16270</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.62%</t>
+          <t>'+1.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.21</v>
+        <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="G11" t="n">
-        <v>231</v>
+        <v>888</v>
       </c>
       <c r="H11" t="n">
-        <v>10.85</v>
+        <v>4.88</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18570</v>
+        <v>16100</v>
       </c>
       <c r="K11" t="n">
-        <v>18740</v>
+        <v>16200</v>
       </c>
       <c r="L11" t="n">
-        <v>18900</v>
+        <v>16750</v>
       </c>
       <c r="M11" t="n">
-        <v>18580</v>
+        <v>15560</v>
       </c>
       <c r="N11" t="n">
-        <v>10.64</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>30769467495</v>
+        <v>269236327740</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-143000</v>
+        <v>-173000</v>
       </c>
       <c r="S11" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6천억 규모 수주 발표에도 주가 약세. 대차해지 운동 관련 논의 활발.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대감. 통신장비 부족 현상과 2만원 목표 주가 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '대차해지', '금리인상']</t>
+          <t>['광통신', '통신장비', '미국주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16360</v>
+        <v>18730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+0.86%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.93</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>854</v>
+        <v>245</v>
       </c>
       <c r="H12" t="n">
-        <v>4.88</v>
+        <v>10.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16100</v>
+        <v>18570</v>
       </c>
       <c r="K12" t="n">
-        <v>16200</v>
+        <v>18740</v>
       </c>
       <c r="L12" t="n">
-        <v>16750</v>
+        <v>18900</v>
       </c>
       <c r="M12" t="n">
-        <v>15560</v>
+        <v>18580</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>10.64</v>
       </c>
       <c r="O12" t="n">
-        <v>261411882000</v>
+        <v>32678378950</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-173000</v>
+        <v>-143000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 수혜 기대감. 통신장비 부족 현상과 2만원 목표 주가 제시.</t>
+          <t>6천억 수주 발표 및 대차해지 운동 언급. 정부의 웨스팅하우스 지분 인수 타진 소식.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '통신장비', '미국주가']</t>
+          <t>['수주', '대차해지', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254500</v>
+        <v>13520</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.39%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>1.36</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>434</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>2208</v>
+        <v>68</v>
       </c>
       <c r="H13" t="n">
-        <v>46.52</v>
+        <v>1.76</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>253500</v>
+        <v>13530</v>
       </c>
       <c r="K13" t="n">
-        <v>257000</v>
+        <v>14280</v>
       </c>
       <c r="L13" t="n">
-        <v>259000</v>
+        <v>14800</v>
       </c>
       <c r="M13" t="n">
-        <v>252000</v>
+        <v>13130</v>
       </c>
       <c r="N13" t="n">
-        <v>46.56</v>
+        <v>0.4</v>
       </c>
       <c r="O13" t="n">
-        <v>951225184000</v>
+        <v>72017960695</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>25700</v>
       </c>
       <c r="Q13" t="n">
-        <v>77100</v>
+        <v>4600</v>
       </c>
       <c r="R13" t="n">
-        <v>-149000</v>
+        <v>2000</v>
       </c>
       <c r="S13" t="n">
-        <v>-85000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 반도체 섹터 상승 모멘텀 분석. 금리 인상 불확실성 해소 및 엔비디아, 마이크론 상승세 연동 가능성 언급.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '금리인상', '모멘텀']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13580</v>
+        <v>253000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.36</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>436</v>
       </c>
       <c r="G14" t="n">
-        <v>68</v>
+        <v>2191</v>
       </c>
       <c r="H14" t="n">
-        <v>1.76</v>
+        <v>46.52</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13530</v>
+        <v>253500</v>
       </c>
       <c r="K14" t="n">
-        <v>14280</v>
+        <v>257000</v>
       </c>
       <c r="L14" t="n">
-        <v>14800</v>
+        <v>259000</v>
       </c>
       <c r="M14" t="n">
-        <v>13130</v>
+        <v>252000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4</v>
+        <v>46.56</v>
       </c>
       <c r="O14" t="n">
-        <v>71242766990</v>
+        <v>1018125269750</v>
       </c>
       <c r="P14" t="n">
-        <v>25700</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>4600</v>
+        <v>77100</v>
       </c>
       <c r="R14" t="n">
-        <v>2000</v>
+        <v>-149000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-85000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등으로 인한 기대감 형성. 일부 긍정적 전망과 함께 주가 부양 의지 및 상승 여력에 대한 논의.</t>
+          <t>정치적 이슈와 금리 인상 관련 언급. 반도체 섹터의 불확실성 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', '미국주가', '목표가']</t>
+          <t>['반도체', '금리인상', '정치']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1755000</v>
+        <v>8430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>89</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="n">
+        <v>202</v>
+      </c>
+      <c r="H15" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>8470</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8470</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8510</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8360</v>
+      </c>
+      <c r="N15" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7978160890</v>
+      </c>
+      <c r="P15" t="n">
+        <v>17950</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>8120</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-169000</v>
+      </c>
+      <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>800</v>
-      </c>
-      <c r="F15" t="n">
-        <v>460</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1477</v>
-      </c>
-      <c r="H15" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1759000</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1770000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1785000</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1735000</v>
-      </c>
-      <c r="N15" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1763426452000</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2987000</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>333000</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-172000</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-24000</v>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>ADR 괴리율 해소 및 자사주 매수 기대감으로 인한 상승 전망. 악재 소멸 후 상승각 논의.</t>
+          <t>중국 디스플레이 산업에 대한 경쟁력 약화 및 높은 부채 비율로 인한 부정적 전망. 경영 능력 의문 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['ADR', '괴리율', '자사주매수']</t>
+          <t>['중국', '영업이익', '부채']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>1748000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.24%</t>
+          <t>'-0.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>464</v>
       </c>
       <c r="G16" t="n">
-        <v>195</v>
+        <v>1476</v>
       </c>
       <c r="H16" t="n">
-        <v>26.54</v>
+        <v>50.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8470</v>
+        <v>1759000</v>
       </c>
       <c r="K16" t="n">
-        <v>8470</v>
+        <v>1770000</v>
       </c>
       <c r="L16" t="n">
-        <v>8510</v>
+        <v>1785000</v>
       </c>
       <c r="M16" t="n">
-        <v>8360</v>
+        <v>1735000</v>
       </c>
       <c r="N16" t="n">
-        <v>26.66</v>
+        <v>50.2</v>
       </c>
       <c r="O16" t="n">
-        <v>7187819275</v>
+        <v>1854716861500</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R16" t="n">
-        <v>-169000</v>
+        <v>-172000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>중국 디스플레이 산업에 대한 경쟁력 약화 및 높은 부채 비율로 인한 부정적 전망. 경영 능력 의문 제기.</t>
+          <t>미국 금리 인상 불확실성 해소 및 자사주 매수 통한 상승 기대. 9월 악재 소멸.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['중국', '영업이익', '부채']</t>
+          <t>['금리인상', '자사주매수', '악재소멸']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3490</v>
+        <v>13830</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.85%</t>
+          <t>'-1.00%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.85</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="H17" t="n">
-        <v>2.26</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3520</v>
+        <v>13970</v>
       </c>
       <c r="K17" t="n">
-        <v>3730</v>
+        <v>13450</v>
       </c>
       <c r="L17" t="n">
-        <v>3750</v>
+        <v>13970</v>
       </c>
       <c r="M17" t="n">
-        <v>3460</v>
+        <v>13410</v>
       </c>
       <c r="N17" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4451141577</v>
+        <v>11269693040</v>
       </c>
       <c r="P17" t="n">
-        <v>16110</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>-276000</v>
+        <v>116000</v>
       </c>
       <c r="S17" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>명확한 근거 없는 하락 및 상폐 우려, 주주들의 부정적 심리 확산.</t>
+          <t>국제 유가 변동성에 따른 단기적 등락 전망. 유가 조정 시 상승, 폭등 시 하락 패턴 반복 예상.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['하락', '상폐', '불확실성']</t>
+          <t>['국제 유가', '유가 변동성', '등락 패턴']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13790</v>
+        <v>3475</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.28%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01</v>
+        <v>-0.85</v>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01</v>
+        <v>2.26</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13970</v>
+        <v>3520</v>
       </c>
       <c r="K18" t="n">
-        <v>13450</v>
+        <v>3730</v>
       </c>
       <c r="L18" t="n">
-        <v>13970</v>
+        <v>3750</v>
       </c>
       <c r="M18" t="n">
-        <v>13410</v>
+        <v>3460</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O18" t="n">
-        <v>10676287705</v>
+        <v>4592615301</v>
       </c>
       <c r="P18" t="n">
-        <v>36200</v>
+        <v>16110</v>
       </c>
       <c r="Q18" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R18" t="n">
-        <v>116000</v>
+        <v>-276000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>국제 유가 변동성에 따른 단기적 등락 전망. 유가 조정 시 상승, 폭등 시 하락 패턴 반복 예상.</t>
+          <t>차익 실현 매물 출회 및 급락 추세. 소식 부재와 무자비한 주가 움직임.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['국제 유가', '유가 변동성', '등락 패턴']</t>
+          <t>['차익실현', '급락', '주가흐름']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -2131,18 +2131,18 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10290</v>
+        <v>10280</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
@@ -2174,7 +2174,7 @@
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>46935321105</v>
+        <v>47960506775</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4190</v>
+        <v>4155</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'-5.78%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>32</v>
       </c>
       <c r="G20" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>32147701440</v>
+        <v>33544331878</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
